--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bremdode\repos\NixieClock\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bremdode\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CA4235B-CDF1-475F-967A-5D080D502F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5993517-CE53-46F4-9A6A-6AE0B853BE2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{CEEDE04D-AA35-43EB-9185-9692CEFE30A3}"/>
+    <workbookView xWindow="-25335" yWindow="3465" windowWidth="21600" windowHeight="11385" xr2:uid="{CEEDE04D-AA35-43EB-9185-9692CEFE30A3}"/>
   </bookViews>
   <sheets>
     <sheet name="nixie_clock_design" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="191">
   <si>
     <t>Reference</t>
   </si>
@@ -530,16 +530,114 @@
   </si>
   <si>
     <t>Connector_USB:USB_C_Receptacle_GCT_USB4105-xx-A_16P_TopMnt_Horizontal</t>
+  </si>
+  <si>
+    <t>LCSC</t>
+  </si>
+  <si>
+    <t>C646051</t>
+  </si>
+  <si>
+    <t>C19110</t>
+  </si>
+  <si>
+    <t>C14663</t>
+  </si>
+  <si>
+    <t>C165101</t>
+  </si>
+  <si>
+    <t>C5674</t>
+  </si>
+  <si>
+    <t>C5189825</t>
+  </si>
+  <si>
+    <t>C85713</t>
+  </si>
+  <si>
+    <t>C1853160</t>
+  </si>
+  <si>
+    <t>C5128373</t>
+  </si>
+  <si>
+    <t>C519405</t>
+  </si>
+  <si>
+    <t>C377089</t>
+  </si>
+  <si>
+    <t>C364563</t>
+  </si>
+  <si>
+    <t>C2981449</t>
+  </si>
+  <si>
+    <t>C2827688</t>
+  </si>
+  <si>
+    <t>C707998</t>
+  </si>
+  <si>
+    <t>C962640</t>
+  </si>
+  <si>
+    <t>C2649922</t>
+  </si>
+  <si>
+    <t>C305412</t>
+  </si>
+  <si>
+    <t>C5224260</t>
+  </si>
+  <si>
+    <t>C123008</t>
+  </si>
+  <si>
+    <t>C273395</t>
+  </si>
+  <si>
+    <t>C7938441</t>
+  </si>
+  <si>
+    <t>C498153</t>
+  </si>
+  <si>
+    <t>C5246810</t>
+  </si>
+  <si>
+    <t>C92253</t>
+  </si>
+  <si>
+    <t>C19949064</t>
+  </si>
+  <si>
+    <t>C580135</t>
+  </si>
+  <si>
+    <t>C179599</t>
+  </si>
+  <si>
+    <t>C3020560</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -562,17 +660,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -603,36 +707,38 @@
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExterneDaten_1" connectionId="1" xr16:uid="{8FFF970C-F459-42ED-91BD-ACBA2FD552F0}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="Reference" tableColumnId="1"/>
       <queryTableField id="2" name="Value" tableColumnId="2"/>
       <queryTableField id="3" name="Footprint" tableColumnId="3"/>
       <queryTableField id="4" name="Qty" tableColumnId="4"/>
       <queryTableField id="5" name="DNP" tableColumnId="5"/>
       <queryTableField id="6" name="MPN" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{17E7BDF9-0AA7-4CB9-9FA0-EF8FDE6C95B7}" name="nixie_clock_design" displayName="nixie_clock_design" ref="A1:F48" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F48" xr:uid="{17E7BDF9-0AA7-4CB9-9FA0-EF8FDE6C95B7}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{30A30195-E10B-4B49-A56A-8F2D5FFA9EAD}" uniqueName="1" name="Reference" queryTableFieldId="1" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{4F38B271-8E8B-4EB6-983E-ED57A77B073A}" uniqueName="2" name="Value" queryTableFieldId="2" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{4CFBDE0F-5D23-4714-837B-2B3885520C3B}" uniqueName="3" name="Footprint" queryTableFieldId="3" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{17E7BDF9-0AA7-4CB9-9FA0-EF8FDE6C95B7}" name="nixie_clock_design" displayName="nixie_clock_design" ref="A1:G48" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G48" xr:uid="{17E7BDF9-0AA7-4CB9-9FA0-EF8FDE6C95B7}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{30A30195-E10B-4B49-A56A-8F2D5FFA9EAD}" uniqueName="1" name="Reference" queryTableFieldId="1" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{4F38B271-8E8B-4EB6-983E-ED57A77B073A}" uniqueName="2" name="Value" queryTableFieldId="2" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{4CFBDE0F-5D23-4714-837B-2B3885520C3B}" uniqueName="3" name="Footprint" queryTableFieldId="3" dataDxfId="3"/>
     <tableColumn id="4" xr3:uid="{E54573E1-7025-4AF6-8D6C-E4BCFD0B9923}" uniqueName="4" name="Qty" queryTableFieldId="4"/>
-    <tableColumn id="5" xr3:uid="{050090FD-383B-4BE7-AFEB-A74D9A98D10A}" uniqueName="5" name="DNP" queryTableFieldId="5" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{32C24F37-1D2F-4EEE-B448-AAA8FF099C47}" uniqueName="6" name="MPN" queryTableFieldId="6" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{050090FD-383B-4BE7-AFEB-A74D9A98D10A}" uniqueName="5" name="DNP" queryTableFieldId="5" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{32C24F37-1D2F-4EEE-B448-AAA8FF099C47}" uniqueName="6" name="MPN" queryTableFieldId="6" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{278F64EA-D68E-472E-84F4-68FA899E4478}" uniqueName="7" name="LCSC" queryTableFieldId="7" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -928,18 +1034,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71A9AF87-D8DE-4BF3-96AE-177B4E936B86}">
-  <dimension ref="A1:F48"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G48"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="51.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="68.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="51.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="68.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -958,8 +1064,11 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -978,8 +1087,11 @@
       <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -998,8 +1110,11 @@
       <c r="F3" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -1018,8 +1133,11 @@
       <c r="F4" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G4" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
@@ -1038,8 +1156,11 @@
       <c r="F5" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G5" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>22</v>
       </c>
@@ -1058,8 +1179,11 @@
       <c r="F6" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G6" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
@@ -1078,8 +1202,11 @@
       <c r="F7" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G7" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>28</v>
       </c>
@@ -1098,8 +1225,11 @@
       <c r="F8" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G8" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>30</v>
       </c>
@@ -1118,8 +1248,11 @@
       <c r="F9" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G9" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>33</v>
       </c>
@@ -1138,8 +1271,11 @@
       <c r="F10" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G10" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>36</v>
       </c>
@@ -1158,8 +1294,11 @@
       <c r="F11" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G11" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>39</v>
       </c>
@@ -1178,8 +1317,11 @@
       <c r="F12" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G12" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>42</v>
       </c>
@@ -1198,8 +1340,11 @@
       <c r="F13" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G13" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>46</v>
       </c>
@@ -1218,8 +1363,11 @@
       <c r="F14" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G14" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>48</v>
       </c>
@@ -1238,8 +1386,11 @@
       <c r="F15" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G15" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>52</v>
       </c>
@@ -1258,8 +1409,11 @@
       <c r="F16" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G16" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>56</v>
       </c>
@@ -1278,8 +1432,11 @@
       <c r="F17" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G17" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>59</v>
       </c>
@@ -1298,8 +1455,11 @@
       <c r="F18" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G18" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>63</v>
       </c>
@@ -1318,8 +1478,9 @@
       <c r="F19" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G19" s="1"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>67</v>
       </c>
@@ -1338,8 +1499,9 @@
       <c r="F20" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G20" s="1"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>70</v>
       </c>
@@ -1358,8 +1520,9 @@
       <c r="F21" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G21" s="1"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>73</v>
       </c>
@@ -1378,8 +1541,11 @@
       <c r="F22" s="1" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G22" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>76</v>
       </c>
@@ -1398,8 +1564,11 @@
       <c r="F23" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G23" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>79</v>
       </c>
@@ -1418,8 +1587,11 @@
       <c r="F24" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G24" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>83</v>
       </c>
@@ -1438,8 +1610,9 @@
       <c r="F25" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G25" s="1"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>87</v>
       </c>
@@ -1458,8 +1631,9 @@
       <c r="F26" s="1" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G26" s="1"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>91</v>
       </c>
@@ -1478,8 +1652,9 @@
       <c r="F27" s="1" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G27" s="1"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>94</v>
       </c>
@@ -1498,8 +1673,9 @@
       <c r="F28" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G28" s="1"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>97</v>
       </c>
@@ -1518,8 +1694,9 @@
       <c r="F29" s="1" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G29" s="1"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>101</v>
       </c>
@@ -1538,8 +1715,9 @@
       <c r="F30" s="1" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G30" s="1"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>104</v>
       </c>
@@ -1558,8 +1736,9 @@
       <c r="F31" s="1" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G31" s="1"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>105</v>
       </c>
@@ -1578,8 +1757,9 @@
       <c r="F32" s="1" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G32" s="1"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>108</v>
       </c>
@@ -1598,8 +1778,9 @@
       <c r="F33" s="1" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G33" s="1"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>111</v>
       </c>
@@ -1618,8 +1799,9 @@
       <c r="F34" s="1" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G34" s="1"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>114</v>
       </c>
@@ -1638,8 +1820,9 @@
       <c r="F35" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G35" s="1"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>117</v>
       </c>
@@ -1658,8 +1841,9 @@
       <c r="F36" s="1" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G36" s="1"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>120</v>
       </c>
@@ -1678,8 +1862,9 @@
       <c r="F37" s="1" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G37" s="1"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>123</v>
       </c>
@@ -1698,8 +1883,9 @@
       <c r="F38" s="1" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G38" s="1"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>126</v>
       </c>
@@ -1718,8 +1904,11 @@
       <c r="F39" s="1" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G39" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>129</v>
       </c>
@@ -1738,8 +1927,11 @@
       <c r="F40" s="1" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G40" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>132</v>
       </c>
@@ -1758,8 +1950,11 @@
       <c r="F41" s="1" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G41" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>136</v>
       </c>
@@ -1778,8 +1973,11 @@
       <c r="F42" s="1" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G42" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>140</v>
       </c>
@@ -1798,8 +1996,11 @@
       <c r="F43" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G43" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>144</v>
       </c>
@@ -1818,8 +2019,11 @@
       <c r="F44" s="1" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G44" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>148</v>
       </c>
@@ -1838,8 +2042,11 @@
       <c r="F45" s="1" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G45" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>152</v>
       </c>
@@ -1858,8 +2065,11 @@
       <c r="F46" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G46" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>155</v>
       </c>
@@ -1878,8 +2088,11 @@
       <c r="F47" s="1" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G47" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>158</v>
       </c>
@@ -1898,12 +2111,47 @@
       <c r="F48" s="1" t="s">
         <v>159</v>
       </c>
+      <c r="G48" s="2" t="s">
+        <v>190</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G41" r:id="rId1" display="https://www.lcsc.com/product-detail/Shift-Registers_Microchip-Tech-HV5122PJ-G_C646051.html" xr:uid="{E304AF9D-1087-4571-8E57-93DBCBD05C62}"/>
+    <hyperlink ref="G2" r:id="rId2" display="https://www.lcsc.com/product-detail/Multilayer-Ceramic-Capacitors-MLCC-SMD-SMT_Samsung-Electro-Mechanics-CL21B225KAFNNNE_C19110.html" xr:uid="{FD6CF950-60D1-4FF9-ACF6-99F25D8CBD53}"/>
+    <hyperlink ref="G3" r:id="rId3" display="https://www.lcsc.com/product-detail/Multilayer-Ceramic-Capacitors-MLCC-SMD-SMT_YAGEO-CC0603KRX7R9BB104_C14663.html" xr:uid="{74109004-EDF9-41CC-8B58-E24B19F32363}"/>
+    <hyperlink ref="G4" r:id="rId4" display="https://www.lcsc.com/product-detail/Multilayer-Ceramic-Capacitors-MLCC-SMD-SMT_FH-Guangdong-Fenghua-Advanced-Tech-1206B106K100NT_C165101.html" xr:uid="{B93989DF-8DD4-49CB-9A2A-81B54DE155A9}"/>
+    <hyperlink ref="G5" r:id="rId5" display="https://www.lcsc.com/product-detail/Multilayer-Ceramic-Capacitors-MLCC-SMD-SMT_Samsung-Electro-Mechanics-CL21A226MQQNNNE_C5674.html" xr:uid="{BB99BECD-1199-4533-A789-5F6241E0E849}"/>
+    <hyperlink ref="G6" r:id="rId6" display="https://www.lcsc.com/product-detail/Multilayer-Ceramic-Capacitors-MLCC-SMD-SMT_Samwha-Capacitor-CS3225X7R476K100NRL_C5189825.html" xr:uid="{B5B3B724-D833-4FA5-B07E-FF4A455533BB}"/>
+    <hyperlink ref="G7" r:id="rId7" display="https://www.lcsc.com/product-detail/Multilayer-Ceramic-Capacitors-MLCC-SMD-SMT_Samsung-Electro-Mechanics-CL10A106MP8NNNC_C85713.html" xr:uid="{329CA584-C658-4EAE-B69F-A3CB595A3410}"/>
+    <hyperlink ref="G8" r:id="rId8" display="https://www.lcsc.com/product-detail/Multilayer-Ceramic-Capacitors-MLCC-SMD-SMT_YAGEO-CC0603KRX7R9BB104_C14663.html" xr:uid="{F4A32187-21BB-4DB4-A1FC-E19BCFC91C1A}"/>
+    <hyperlink ref="G9" r:id="rId9" display="https://www.lcsc.com/product-detail/Multilayer-Ceramic-Capacitors-MLCC-SMD-SMT_YAGEO-CC0603JRNPO6BN101_C1853160.html" xr:uid="{7111B3B7-407A-4899-A656-DFDCD721E0C2}"/>
+    <hyperlink ref="G10" r:id="rId10" display="https://www.lcsc.com/product-detail/Multilayer-Ceramic-Capacitors-MLCC-SMD-SMT_Kyocera-AVX-0603ZC223KAT2A_C5128373.html" xr:uid="{A7648EE4-2A14-49B0-87D3-0832C68BE011}"/>
+    <hyperlink ref="G11" r:id="rId11" display="https://www.lcsc.com/product-detail/Multilayer-Ceramic-Capacitors-MLCC-SMD-SMT_YAGEO-CC0603KRX7R6BB103_C519405.html" xr:uid="{A4CA6C9D-E4E5-4AEB-BE85-5F2FF2451F34}"/>
+    <hyperlink ref="G12" r:id="rId12" display="https://www.lcsc.com/product-detail/Multilayer-Ceramic-Capacitors-MLCC-SMD-SMT_CCTC-TCC1206X7R224K251HT_C377089.html" xr:uid="{19E6DA67-2CF6-455B-9754-95946FF2624C}"/>
+    <hyperlink ref="G13" r:id="rId13" display="https://www.lcsc.com/product-detail/LED-Indication-Discrete_Lite-On-LTST-C150TGKT_C364563.html" xr:uid="{FF7B9BCB-9C46-4E85-8B75-78084D10CADF}"/>
+    <hyperlink ref="G14" r:id="rId14" display="https://www.lcsc.com/product-detail/LED-Indication-Discrete_PARALIGHT-L-C150SRCT_C2981449.html" xr:uid="{C3056B4C-8D9A-4CB9-99D5-D19F825D0F21}"/>
+    <hyperlink ref="G15" r:id="rId15" display="https://www.lcsc.com/product-detail/ESD-and-Surge-Protection-TVS-ESD_TECH-PUBLIC-PRTR5V0U2X_C2827688.html" xr:uid="{5A78AD1E-3618-4509-BFE8-AEF4722AD412}"/>
+    <hyperlink ref="G16" r:id="rId16" display="https://www.lcsc.com/product-detail/ESD-and-Surge-Protection-TVS-ESD_FTR-P6SMB6-8A_C707998.html" xr:uid="{E6C053BA-017B-442A-9CAE-851948FFAF79}"/>
+    <hyperlink ref="G17" r:id="rId17" display="https://www.lcsc.com/product-detail/Fast-Recovery-High-Efficiency-Diodes_ROHM-Semicon-RFN1LAM6STR_C962640.html" xr:uid="{7E9860F1-27D9-4279-B476-C2048EDF4335}"/>
+    <hyperlink ref="G18" r:id="rId18" display="https://www.lcsc.com/product-detail/Resettable-Fuses_Littelfuse-MINISMDC110F-24-2_C2649922.html" xr:uid="{8D2E3EAB-FD54-4076-B603-9060B5925EED}"/>
+    <hyperlink ref="G22" r:id="rId19" display="https://www.lcsc.com/product-detail/Bipolar-BJT_Foshan-Blue-Rocket-Elec-MPSA92_C305412.html" xr:uid="{4D5159A8-A46E-4674-900F-1E97327AF5F0}"/>
+    <hyperlink ref="G23" r:id="rId20" display="https://www.lcsc.com/product-detail/MOSFETs_ElecSuper-BSS138_C5224260.html" xr:uid="{9C0EE2AB-D0C0-4024-9046-18F6E2139167}"/>
+    <hyperlink ref="G24" r:id="rId21" display="https://www.lcsc.com/product-detail/Digital-Transistors_ROHM-Semicon-UMH3NTN_C123008.html" xr:uid="{1FC9FF41-989B-4DB5-8EDB-0944E1FD4103}"/>
+    <hyperlink ref="G39" r:id="rId22" display="https://www.lcsc.com/product-detail/Slide-Switches_E-Switch-EG1224_C273395.html" xr:uid="{6A4055C8-9DE5-46EE-8B66-A3721BA64652}"/>
+    <hyperlink ref="G40" r:id="rId23" display="https://www.lcsc.com/product-detail/Audio-Transformers_Coilcraft-DA2032-ALD_C7938441.html" xr:uid="{A0251971-896A-4537-90E0-3A7EFD5246DC}"/>
+    <hyperlink ref="G42" r:id="rId24" display="https://www.lcsc.com/product-detail/Voltage-Regulators-Linear-Low-Drop-Out-LDO-Regulators_HGSEMI-LM1117MP-3-3-TR_C498153.html" xr:uid="{E7A6C4DE-90D6-4F8D-A7F7-AD17600A7985}"/>
+    <hyperlink ref="G43" r:id="rId25" display="https://www.lcsc.com/product-detail/USB-Converters_FTDI-FT232RNL-REEL_C5246810.html" xr:uid="{C7527F3D-F716-492B-A8CB-A1FD671AAEC1}"/>
+    <hyperlink ref="G44" r:id="rId26" display="https://www.lcsc.com/product-detail/I-O-Expanders_Microchip-Tech-MCP23008-E-SO_C92253.html" xr:uid="{08EA8AB3-B718-4531-AA01-5ADDF317C3ED}"/>
+    <hyperlink ref="G45" r:id="rId27" display="https://www.lcsc.com/product-detail/WiFi-Modules_DOIT-ESP-12F_C19949064.html" xr:uid="{F5FDF142-C739-4318-8FDD-72D6FCF2FB3D}"/>
+    <hyperlink ref="G46" r:id="rId28" display="https://www.lcsc.com/product-detail/DC-DC-Converters_Analog-Devices-LT3757EMSE-TRPBF_C580135.html" xr:uid="{B1D361F0-EF94-4457-B6EA-63BBFA70F553}"/>
+    <hyperlink ref="G47" r:id="rId29" display="https://www.lcsc.com/product-detail/Voltage-Regulators-Linear-Low-Drop-Out-LDO-Regulators_onsemi-NCV1117ST12T3G_C179599.html" xr:uid="{978B709F-DD52-4E22-B18E-FE345474DEBD}"/>
+    <hyperlink ref="G48" r:id="rId30" display="https://www.lcsc.com/product-detail/span-style-background-color-ff0-USB-span-Connectors_Global-Connector-Technology-USB4105-GF-A_C3020560.html" xr:uid="{4620F6C4-A397-4840-B533-DEF8E89EBB1E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId31"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId32"/>
   </tableParts>
 </worksheet>
 </file>
